--- a/assets/temp-before abbreviation work.xlsx
+++ b/assets/temp-before abbreviation work.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jared\source\repos\avtopia\data_sync_desktop\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6439DE2-1A60-4140-9BE3-D23104905161}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B0F3C2A2-9B87-48AA-94F1-CFDC4892C799}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28740" yWindow="4185" windowWidth="21600" windowHeight="11385" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7572" uniqueCount="2849">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7572" uniqueCount="2851">
   <si>
     <t>ID</t>
   </si>
@@ -8586,6 +8586,12 @@
   </si>
   <si>
     <t>Bethel, AK 99559, USA</t>
+  </si>
+  <si>
+    <t>2010 Airport Rd PO Box 9248</t>
+  </si>
+  <si>
+    <t>2000 Sierra Point Pkwy Suite 200</t>
   </si>
 </sst>
 </file>
@@ -35740,7 +35746,7 @@
         <v>1609</v>
       </c>
       <c r="F260" s="5" t="s">
-        <v>1610</v>
+        <v>2850</v>
       </c>
       <c r="H260" s="5" t="s">
         <v>1611</v>
@@ -35879,7 +35885,7 @@
         <v>1620</v>
       </c>
       <c r="F262" s="5" t="s">
-        <v>1621</v>
+        <v>2849</v>
       </c>
       <c r="G262" s="3" t="s">
         <v>1622</v>
